--- a/lista_apoio_backup.xlsx
+++ b/lista_apoio_backup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Nome do Técnico</t>
+          <t>Nome do T?cnico</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Selecione o tópico</t>
+          <t>Selecione o t?pico</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,12 +439,140 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Situação</t>
+          <t>Situa??o</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Responsável/Apoio</t>
+          <t>Respons?vel/Apoio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:22:26</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anna Luiza Rezende Tavares</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Altera??o Salarial</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Parcela de altera??o retroativa calculando a maior e em uma ?nica parcela</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Luma</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:33:50</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Clessiane Pereira Dos Santos</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F?rmula</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Rubrica com f?rmula n?o atende aos comandos para calcular corretamente</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Luma</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:41:08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Michelle G Santos</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FGTS Digital</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FGTS diferente entre o portal do FGTS e o sistema</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Em an?lise</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:46:21</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Emilly Caylane Costa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Configura??o de Rubrica</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rubrica de vale transporte</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Em an?lise</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brenda</t>
         </is>
       </c>
     </row>

--- a/lista_apoio_backup.xlsx
+++ b/lista_apoio_backup.xlsx
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Nome do T?cnico</t>
+          <t>Nome do Técnico</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Selecione o t?pico</t>
+          <t>Selecione o tópico</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Situa??o</t>
+          <t>Situação</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Respons?vel/Apoio</t>
+          <t>Responsável/Apoio</t>
         </is>
       </c>
     </row>

--- a/lista_apoio_backup.xlsx
+++ b/lista_apoio_backup.xlsx
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Nome do Técnico</t>
+          <t>Nome do T?cnico</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Selecione o tópico</t>
+          <t>Selecione o t?pico</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Situação</t>
+          <t>Situa??o</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Responsável/Apoio</t>
+          <t>Respons?vel/Apoio</t>
         </is>
       </c>
     </row>

--- a/lista_apoio_backup.xlsx
+++ b/lista_apoio_backup.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Nome do Técnico</t>
+          <t>Nome do T?cnico</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Selecione o tópico</t>
+          <t>Selecione o t?pico</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Situação</t>
+          <t>Situa??o</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Responsável/Apoio</t>
+          <t>Respons?vel/Apoio</t>
         </is>
       </c>
     </row>
@@ -454,31 +454,15 @@
           <t>02/06/2026 08:22:26</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anna Luiza Rezende Tavares</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Altera??o Salarial</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Parcela de altera??o retroativa calculando a maior e em uma ?nica parcela</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Luma</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,31 +470,15 @@
           <t>02/06/2026 08:33:50</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Clessiane Pereira Dos Santos</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>F?rmula</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Rubrica com f?rmula n?o atende aos comandos para calcular corretamente</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Finalizado</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Luma</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -518,31 +486,15 @@
           <t>02/06/2026 08:41:08</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Michelle G Santos</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>FGTS Digital</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>FGTS diferente entre o portal do FGTS e o sistema</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Em an?lise</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Brenda</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,29 +502,237 @@
           <t>02/06/2026 08:46:21</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Emilly Caylane Costa</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Configura??o de Rubrica</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>rubrica de vale transporte</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:22:26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Parcela de altera??o retroativa calculando a maior e em uma ?nica parcela</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:33:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rubrica com f?rmula n?o atende aos comandos para calcular corretamente</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:41:08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FGTS diferente entre o portal do FGTS e o sistema</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>02/06/2026 08:46:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>rubrica de vale transporte</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>05/06/2026 14:23:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Damyllis Lorraine De Oliveira Gon?alves</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13? Sal?rio</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Relat?rios admissionais apresentando erro - sem dados, apenas em uma empresa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Em an?lise</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Luma</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>05/06/2026 14:26:08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gabriel Gomes De Andrade</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13? Sal?rio</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Duvida maternidade</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Finalizado</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Brenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>05/06/2026 14:55:54</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Pedro Luiz Mota Sousa</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Folha Mensal</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Calculo de diferen?a de m?dia de f?rias em folha</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Em an?lise</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brenda</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>05/06/2026 15:06:33</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anna Luiza Rezende Tavares</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Emprestimo consignado calculando parcela indevida</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Em an?lise</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Luma</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>05/06/2026 15:07:04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lizandra Gomes Duarte</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Rescis?o</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Oi, boa tarde.. Ao transferir um func de uma empresa para a outra, o correto e unifica</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Em an?lise</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Luma</t>
         </is>
       </c>
     </row>
